--- a/01_data/01_input_data/01_raw/01_Russian_War_Case/nrg_cb_gasm__custom_15468335_page_spreadsheet.xlsx
+++ b/01_data/01_input_data/01_raw/01_Russian_War_Case/nrg_cb_gasm__custom_15468335_page_spreadsheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\01_raw\01_Russian_War_Case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476A3C90-919D-4A1B-AD81-986EE018BDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC870681-5983-4403-ABEF-7E7982891C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,9 +371,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.##########"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -475,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -526,10 +527,10 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -538,6 +539,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7391,7 +7395,7 @@
       <c r="X47" s="14">
         <v>5.016</v>
       </c>
-      <c r="Y47" s="7">
+      <c r="Y47" s="23">
         <f t="shared" si="0"/>
         <v>56.895000000000003</v>
       </c>
@@ -8122,6 +8126,21 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="AB10:AC10"/>
+    <mergeCell ref="AD10:AE10"/>
     <mergeCell ref="AP10:AQ10"/>
     <mergeCell ref="AR10:AS10"/>
     <mergeCell ref="AT10:AU10"/>
@@ -8131,21 +8150,6 @@
     <mergeCell ref="AJ10:AK10"/>
     <mergeCell ref="AL10:AM10"/>
     <mergeCell ref="AN10:AO10"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="AB10:AC10"/>
-    <mergeCell ref="AD10:AE10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
